--- a/sim/CLEAN_sigma_chol_outcomes.xlsx
+++ b/sim/CLEAN_sigma_chol_outcomes.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
-    <t>Calibration outcomes for sigma under chol parameterizatio</t>
+    <t>Calibration outcomes for sigma under cholesky parameterization</t>
   </si>
   <si>
     <t>True sigma_m (bps)</t>
